--- a/Data/Patching/VTA_diet.xlsx
+++ b/Data/Patching/VTA_diet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Patching\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2304776156689/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1A6BC64-9717-46A5-8E68-FD6D4F540470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_DD44812713CB06557EABE57933A4161594E5840E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2417130-ADFA-4719-9CFD-7595AA271DD0}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="14505" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" r:id="rId1"/>
@@ -764,7 +764,7 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -778,7 +778,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -792,7 +792,7 @@
         <v>17.391304347826093</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,7 +806,7 @@
         <v>17.129629629629626</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,7 +821,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,7 +836,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -851,7 +851,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -881,7 +881,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -911,7 +911,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
